--- a/DBs/nfl/Results/NFL_2023_Results.xlsx
+++ b/DBs/nfl/Results/NFL_2023_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\TracerProjects2\NFL_Elo\Results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjsut\tracersports-app\DBs\nfl\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{359DB757-BBD7-4944-8885-9D722E3431F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F9B2D8E-EE2F-48F5-97CE-00491B1BFE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{64CD6F09-243A-4ABA-8421-C5E0505218AB}"/>
   </bookViews>
@@ -124,25 +124,16 @@
     <t>CHI</t>
   </si>
   <si>
-    <t>OAK</t>
-  </si>
-  <si>
     <t>DEN</t>
   </si>
   <si>
     <t>MIA</t>
   </si>
   <si>
-    <t>SD</t>
-  </si>
-  <si>
     <t>PHI</t>
   </si>
   <si>
     <t>NE</t>
-  </si>
-  <si>
-    <t>STL</t>
   </si>
   <si>
     <t>SEA</t>
@@ -176,6 +167,15 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>LAC</t>
+  </si>
+  <si>
+    <t>LAR</t>
+  </si>
+  <si>
+    <t>LV</t>
   </si>
 </sst>
 </file>
@@ -1709,10 +1709,10 @@
         <v>11</v>
       </c>
       <c r="E22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" t="s">
         <v>34</v>
-      </c>
-      <c r="F22" t="s">
-        <v>35</v>
       </c>
       <c r="G22" t="s">
         <v>14</v>
@@ -1741,10 +1741,10 @@
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
@@ -1773,10 +1773,10 @@
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G24" t="s">
         <v>14</v>
@@ -1805,10 +1805,10 @@
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
@@ -1837,10 +1837,10 @@
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G26" t="s">
         <v>14</v>
@@ -1869,10 +1869,10 @@
         <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
@@ -1901,10 +1901,10 @@
         <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G28" t="s">
         <v>14</v>
@@ -1933,10 +1933,10 @@
         <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F29" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
@@ -1965,10 +1965,10 @@
         <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F30" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G30" t="s">
         <v>14</v>
@@ -1997,10 +1997,10 @@
         <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F31" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G31" t="s">
         <v>15</v>
@@ -2029,10 +2029,10 @@
         <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
@@ -2061,10 +2061,10 @@
         <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G33" t="s">
         <v>14</v>
@@ -2093,7 +2093,7 @@
         <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F34" t="s">
         <v>27</v>
@@ -2128,7 +2128,7 @@
         <v>27</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G35" t="s">
         <v>14</v>
@@ -2221,10 +2221,10 @@
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F38" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
@@ -2253,10 +2253,10 @@
         <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F39" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G39" t="s">
         <v>14</v>
@@ -2477,7 +2477,7 @@
         <v>11</v>
       </c>
       <c r="E46" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F46" t="s">
         <v>12</v>
@@ -2512,7 +2512,7 @@
         <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G47" t="s">
         <v>15</v>
@@ -2608,7 +2608,7 @@
         <v>29</v>
       </c>
       <c r="F50" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G50" t="s">
         <v>15</v>
@@ -2637,7 +2637,7 @@
         <v>11</v>
       </c>
       <c r="E51" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F51" t="s">
         <v>29</v>
@@ -2669,7 +2669,7 @@
         <v>11</v>
       </c>
       <c r="E52" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F52" t="s">
         <v>23</v>
@@ -2704,7 +2704,7 @@
         <v>23</v>
       </c>
       <c r="F53" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G53" t="s">
         <v>15</v>
@@ -2736,7 +2736,7 @@
         <v>30</v>
       </c>
       <c r="F54" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G54" t="s">
         <v>14</v>
@@ -2765,7 +2765,7 @@
         <v>11</v>
       </c>
       <c r="E55" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F55" t="s">
         <v>30</v>
@@ -2797,10 +2797,10 @@
         <v>11</v>
       </c>
       <c r="E56" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F56" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G56" t="s">
         <v>15</v>
@@ -2829,10 +2829,10 @@
         <v>11</v>
       </c>
       <c r="E57" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F57" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G57" t="s">
         <v>14</v>
@@ -2864,7 +2864,7 @@
         <v>22</v>
       </c>
       <c r="F58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G58" t="s">
         <v>14</v>
@@ -2893,7 +2893,7 @@
         <v>11</v>
       </c>
       <c r="E59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F59" t="s">
         <v>22</v>
@@ -2925,10 +2925,10 @@
         <v>11</v>
       </c>
       <c r="E60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F60" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G60" t="s">
         <v>14</v>
@@ -2957,10 +2957,10 @@
         <v>11</v>
       </c>
       <c r="E61" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F61" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G61" t="s">
         <v>15</v>
@@ -3120,7 +3120,7 @@
         <v>30</v>
       </c>
       <c r="F66" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G66" t="s">
         <v>15</v>
@@ -3149,7 +3149,7 @@
         <v>11</v>
       </c>
       <c r="E67" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F67" t="s">
         <v>30</v>
@@ -3245,7 +3245,7 @@
         <v>11</v>
       </c>
       <c r="E70" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F70" t="s">
         <v>22</v>
@@ -3280,7 +3280,7 @@
         <v>22</v>
       </c>
       <c r="F71" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G71" t="s">
         <v>15</v>
@@ -3437,10 +3437,10 @@
         <v>11</v>
       </c>
       <c r="E76" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F76" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G76" t="s">
         <v>15</v>
@@ -3469,10 +3469,10 @@
         <v>11</v>
       </c>
       <c r="E77" t="s">
+        <v>34</v>
+      </c>
+      <c r="F77" t="s">
         <v>35</v>
-      </c>
-      <c r="F77" t="s">
-        <v>36</v>
       </c>
       <c r="G77" t="s">
         <v>14</v>
@@ -3629,7 +3629,7 @@
         <v>11</v>
       </c>
       <c r="E82" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F82" t="s">
         <v>27</v>
@@ -3664,7 +3664,7 @@
         <v>27</v>
       </c>
       <c r="F83" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G83" t="s">
         <v>15</v>
@@ -3693,10 +3693,10 @@
         <v>11</v>
       </c>
       <c r="E84" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F84" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G84" t="s">
         <v>14</v>
@@ -3725,10 +3725,10 @@
         <v>11</v>
       </c>
       <c r="E85" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F85" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G85" t="s">
         <v>15</v>
@@ -3757,7 +3757,7 @@
         <v>11</v>
       </c>
       <c r="E86" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F86" t="s">
         <v>17</v>
@@ -3792,7 +3792,7 @@
         <v>17</v>
       </c>
       <c r="F87" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G87" t="s">
         <v>14</v>
@@ -3888,7 +3888,7 @@
         <v>23</v>
       </c>
       <c r="F90" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G90" t="s">
         <v>15</v>
@@ -3917,7 +3917,7 @@
         <v>11</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F91" t="s">
         <v>23</v>
@@ -3952,7 +3952,7 @@
         <v>31</v>
       </c>
       <c r="F92" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G92" t="s">
         <v>14</v>
@@ -3981,7 +3981,7 @@
         <v>11</v>
       </c>
       <c r="E93" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F93" t="s">
         <v>31</v>
@@ -4013,7 +4013,7 @@
         <v>11</v>
       </c>
       <c r="E94" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F94" t="s">
         <v>26</v>
@@ -4048,7 +4048,7 @@
         <v>26</v>
       </c>
       <c r="F95" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G95" t="s">
         <v>15</v>
@@ -4080,7 +4080,7 @@
         <v>19</v>
       </c>
       <c r="F96" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G96" t="s">
         <v>15</v>
@@ -4109,7 +4109,7 @@
         <v>11</v>
       </c>
       <c r="E97" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F97" t="s">
         <v>19</v>
@@ -4269,10 +4269,10 @@
         <v>11</v>
       </c>
       <c r="E102" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F102" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G102" t="s">
         <v>15</v>
@@ -4301,10 +4301,10 @@
         <v>11</v>
       </c>
       <c r="E103" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F103" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G103" t="s">
         <v>14</v>
@@ -4397,7 +4397,7 @@
         <v>11</v>
       </c>
       <c r="E106" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F106" t="s">
         <v>33</v>
@@ -4432,7 +4432,7 @@
         <v>33</v>
       </c>
       <c r="F107" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G107" t="s">
         <v>15</v>
@@ -4589,7 +4589,7 @@
         <v>11</v>
       </c>
       <c r="E112" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F112" t="s">
         <v>21</v>
@@ -4624,7 +4624,7 @@
         <v>21</v>
       </c>
       <c r="F113" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G113" t="s">
         <v>15</v>
@@ -4781,7 +4781,7 @@
         <v>11</v>
       </c>
       <c r="E118" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F118" t="s">
         <v>22</v>
@@ -4816,7 +4816,7 @@
         <v>22</v>
       </c>
       <c r="F119" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G119" t="s">
         <v>14</v>
@@ -4845,10 +4845,10 @@
         <v>11</v>
       </c>
       <c r="E120" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F120" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G120" t="s">
         <v>15</v>
@@ -4877,10 +4877,10 @@
         <v>11</v>
       </c>
       <c r="E121" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F121" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G121" t="s">
         <v>14</v>
@@ -4973,10 +4973,10 @@
         <v>11</v>
       </c>
       <c r="E124" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F124" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G124" t="s">
         <v>15</v>
@@ -5005,10 +5005,10 @@
         <v>11</v>
       </c>
       <c r="E125" t="s">
+        <v>37</v>
+      </c>
+      <c r="F125" t="s">
         <v>39</v>
-      </c>
-      <c r="F125" t="s">
-        <v>42</v>
       </c>
       <c r="G125" t="s">
         <v>14</v>
@@ -5040,7 +5040,7 @@
         <v>13</v>
       </c>
       <c r="F126" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G126" t="s">
         <v>14</v>
@@ -5069,7 +5069,7 @@
         <v>11</v>
       </c>
       <c r="E127" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F127" t="s">
         <v>13</v>
@@ -5101,10 +5101,10 @@
         <v>11</v>
       </c>
       <c r="E128" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F128" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G128" t="s">
         <v>14</v>
@@ -5133,10 +5133,10 @@
         <v>11</v>
       </c>
       <c r="E129" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F129" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G129" t="s">
         <v>15</v>
@@ -5232,7 +5232,7 @@
         <v>20</v>
       </c>
       <c r="F132" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G132" t="s">
         <v>14</v>
@@ -5261,7 +5261,7 @@
         <v>11</v>
       </c>
       <c r="E133" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F133" t="s">
         <v>20</v>
@@ -5485,10 +5485,10 @@
         <v>11</v>
       </c>
       <c r="E140" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F140" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G140" t="s">
         <v>15</v>
@@ -5517,10 +5517,10 @@
         <v>11</v>
       </c>
       <c r="E141" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F141" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G141" t="s">
         <v>14</v>
@@ -5552,7 +5552,7 @@
         <v>28</v>
       </c>
       <c r="F142" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G142" t="s">
         <v>14</v>
@@ -5581,7 +5581,7 @@
         <v>11</v>
       </c>
       <c r="E143" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F143" t="s">
         <v>28</v>
@@ -5741,10 +5741,10 @@
         <v>11</v>
       </c>
       <c r="E148" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F148" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G148" t="s">
         <v>14</v>
@@ -5773,10 +5773,10 @@
         <v>11</v>
       </c>
       <c r="E149" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F149" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G149" t="s">
         <v>15</v>
@@ -5805,10 +5805,10 @@
         <v>11</v>
       </c>
       <c r="E150" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F150" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G150" t="s">
         <v>14</v>
@@ -5837,10 +5837,10 @@
         <v>11</v>
       </c>
       <c r="E151" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F151" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G151" t="s">
         <v>15</v>
@@ -5936,7 +5936,7 @@
         <v>30</v>
       </c>
       <c r="F154" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G154" t="s">
         <v>15</v>
@@ -5965,7 +5965,7 @@
         <v>11</v>
       </c>
       <c r="E155" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F155" t="s">
         <v>30</v>
@@ -5997,7 +5997,7 @@
         <v>11</v>
       </c>
       <c r="E156" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F156" t="s">
         <v>32</v>
@@ -6032,7 +6032,7 @@
         <v>32</v>
       </c>
       <c r="F157" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G157" t="s">
         <v>14</v>
@@ -6064,7 +6064,7 @@
         <v>13</v>
       </c>
       <c r="F158" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G158" t="s">
         <v>15</v>
@@ -6093,7 +6093,7 @@
         <v>11</v>
       </c>
       <c r="E159" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F159" t="s">
         <v>13</v>
@@ -6317,7 +6317,7 @@
         <v>11</v>
       </c>
       <c r="E166" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F166" t="s">
         <v>17</v>
@@ -6352,7 +6352,7 @@
         <v>17</v>
       </c>
       <c r="F167" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G167" t="s">
         <v>14</v>
@@ -6448,7 +6448,7 @@
         <v>19</v>
       </c>
       <c r="F170" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G170" t="s">
         <v>15</v>
@@ -6477,7 +6477,7 @@
         <v>11</v>
       </c>
       <c r="E171" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F171" t="s">
         <v>19</v>
@@ -6637,10 +6637,10 @@
         <v>11</v>
       </c>
       <c r="E176" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F176" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G176" t="s">
         <v>15</v>
@@ -6669,10 +6669,10 @@
         <v>11</v>
       </c>
       <c r="E177" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F177" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G177" t="s">
         <v>14</v>
@@ -6701,7 +6701,7 @@
         <v>11</v>
       </c>
       <c r="E178" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F178" t="s">
         <v>23</v>
@@ -6736,7 +6736,7 @@
         <v>23</v>
       </c>
       <c r="F179" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G179" t="s">
         <v>14</v>
@@ -6829,10 +6829,10 @@
         <v>11</v>
       </c>
       <c r="E182" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F182" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G182" t="s">
         <v>15</v>
@@ -6861,10 +6861,10 @@
         <v>11</v>
       </c>
       <c r="E183" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F183" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G183" t="s">
         <v>14</v>
@@ -6893,10 +6893,10 @@
         <v>11</v>
       </c>
       <c r="E184" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F184" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G184" t="s">
         <v>15</v>
@@ -6925,10 +6925,10 @@
         <v>11</v>
       </c>
       <c r="E185" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F185" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G185" t="s">
         <v>14</v>
@@ -6957,10 +6957,10 @@
         <v>11</v>
       </c>
       <c r="E186" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F186" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G186" t="s">
         <v>14</v>
@@ -6989,10 +6989,10 @@
         <v>11</v>
       </c>
       <c r="E187" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F187" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G187" t="s">
         <v>15</v>
@@ -7213,10 +7213,10 @@
         <v>11</v>
       </c>
       <c r="E194" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F194" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G194" t="s">
         <v>15</v>
@@ -7245,10 +7245,10 @@
         <v>11</v>
       </c>
       <c r="E195" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F195" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G195" t="s">
         <v>14</v>
@@ -7280,7 +7280,7 @@
         <v>33</v>
       </c>
       <c r="F196" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G196" t="s">
         <v>15</v>
@@ -7309,7 +7309,7 @@
         <v>11</v>
       </c>
       <c r="E197" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F197" t="s">
         <v>33</v>
@@ -7405,7 +7405,7 @@
         <v>11</v>
       </c>
       <c r="E200" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F200" t="s">
         <v>22</v>
@@ -7440,7 +7440,7 @@
         <v>22</v>
       </c>
       <c r="F201" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G201" t="s">
         <v>14</v>
@@ -7472,7 +7472,7 @@
         <v>31</v>
       </c>
       <c r="F202" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G202" t="s">
         <v>14</v>
@@ -7501,7 +7501,7 @@
         <v>11</v>
       </c>
       <c r="E203" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F203" t="s">
         <v>31</v>
@@ -7533,7 +7533,7 @@
         <v>11</v>
       </c>
       <c r="E204" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F204" t="s">
         <v>23</v>
@@ -7568,7 +7568,7 @@
         <v>23</v>
       </c>
       <c r="F205" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G205" t="s">
         <v>14</v>
@@ -7597,7 +7597,7 @@
         <v>11</v>
       </c>
       <c r="E206" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F206" t="s">
         <v>32</v>
@@ -7632,7 +7632,7 @@
         <v>32</v>
       </c>
       <c r="F207" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G207" t="s">
         <v>14</v>
@@ -7664,7 +7664,7 @@
         <v>13</v>
       </c>
       <c r="F208" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G208" t="s">
         <v>15</v>
@@ -7693,7 +7693,7 @@
         <v>11</v>
       </c>
       <c r="E209" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F209" t="s">
         <v>13</v>
@@ -7725,10 +7725,10 @@
         <v>11</v>
       </c>
       <c r="E210" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F210" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G210" t="s">
         <v>15</v>
@@ -7757,10 +7757,10 @@
         <v>11</v>
       </c>
       <c r="E211" t="s">
+        <v>35</v>
+      </c>
+      <c r="F211" t="s">
         <v>36</v>
-      </c>
-      <c r="F211" t="s">
-        <v>38</v>
       </c>
       <c r="G211" t="s">
         <v>14</v>
@@ -7853,7 +7853,7 @@
         <v>11</v>
       </c>
       <c r="E214" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F214" t="s">
         <v>26</v>
@@ -7888,7 +7888,7 @@
         <v>26</v>
       </c>
       <c r="F215" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G215" t="s">
         <v>14</v>
@@ -7981,10 +7981,10 @@
         <v>11</v>
       </c>
       <c r="E218" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F218" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G218" t="s">
         <v>15</v>
@@ -8013,10 +8013,10 @@
         <v>11</v>
       </c>
       <c r="E219" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F219" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G219" t="s">
         <v>14</v>
@@ -8301,10 +8301,10 @@
         <v>11</v>
       </c>
       <c r="E228" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F228" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G228" t="s">
         <v>15</v>
@@ -8333,10 +8333,10 @@
         <v>11</v>
       </c>
       <c r="E229" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F229" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G229" t="s">
         <v>14</v>
@@ -8365,10 +8365,10 @@
         <v>11</v>
       </c>
       <c r="E230" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F230" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G230" t="s">
         <v>14</v>
@@ -8397,10 +8397,10 @@
         <v>11</v>
       </c>
       <c r="E231" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F231" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G231" t="s">
         <v>15</v>
@@ -8429,7 +8429,7 @@
         <v>11</v>
       </c>
       <c r="E232" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F232" t="s">
         <v>22</v>
@@ -8464,7 +8464,7 @@
         <v>22</v>
       </c>
       <c r="F233" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G233" t="s">
         <v>15</v>
@@ -8493,7 +8493,7 @@
         <v>11</v>
       </c>
       <c r="E234" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F234" t="s">
         <v>18</v>
@@ -8528,7 +8528,7 @@
         <v>18</v>
       </c>
       <c r="F235" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G235" t="s">
         <v>14</v>
@@ -8685,7 +8685,7 @@
         <v>11</v>
       </c>
       <c r="E240" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F240" t="s">
         <v>13</v>
@@ -8720,7 +8720,7 @@
         <v>13</v>
       </c>
       <c r="F241" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G241" t="s">
         <v>14</v>
@@ -8749,7 +8749,7 @@
         <v>11</v>
       </c>
       <c r="E242" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F242" t="s">
         <v>33</v>
@@ -8784,7 +8784,7 @@
         <v>33</v>
       </c>
       <c r="F243" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G243" t="s">
         <v>14</v>
@@ -8816,7 +8816,7 @@
         <v>12</v>
       </c>
       <c r="F244" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G244" t="s">
         <v>15</v>
@@ -8845,7 +8845,7 @@
         <v>11</v>
       </c>
       <c r="E245" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F245" t="s">
         <v>12</v>
@@ -8944,7 +8944,7 @@
         <v>13</v>
       </c>
       <c r="F248" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G248" t="s">
         <v>15</v>
@@ -8973,7 +8973,7 @@
         <v>11</v>
       </c>
       <c r="E249" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F249" t="s">
         <v>13</v>
@@ -9072,7 +9072,7 @@
         <v>32</v>
       </c>
       <c r="F252" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G252" t="s">
         <v>15</v>
@@ -9101,7 +9101,7 @@
         <v>11</v>
       </c>
       <c r="E253" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F253" t="s">
         <v>32</v>
@@ -9328,7 +9328,7 @@
         <v>22</v>
       </c>
       <c r="F260" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G260" t="s">
         <v>14</v>
@@ -9357,7 +9357,7 @@
         <v>11</v>
       </c>
       <c r="E261" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F261" t="s">
         <v>22</v>
@@ -9392,7 +9392,7 @@
         <v>24</v>
       </c>
       <c r="F262" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G262" t="s">
         <v>15</v>
@@ -9421,7 +9421,7 @@
         <v>11</v>
       </c>
       <c r="E263" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F263" t="s">
         <v>24</v>
@@ -9517,10 +9517,10 @@
         <v>11</v>
       </c>
       <c r="E266" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F266" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G266" t="s">
         <v>15</v>
@@ -9549,10 +9549,10 @@
         <v>11</v>
       </c>
       <c r="E267" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F267" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G267" t="s">
         <v>14</v>
@@ -9581,10 +9581,10 @@
         <v>11</v>
       </c>
       <c r="E268" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F268" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G268" t="s">
         <v>15</v>
@@ -9613,10 +9613,10 @@
         <v>11</v>
       </c>
       <c r="E269" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F269" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G269" t="s">
         <v>14</v>
@@ -9648,7 +9648,7 @@
         <v>19</v>
       </c>
       <c r="F270" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G270" t="s">
         <v>15</v>
@@ -9677,7 +9677,7 @@
         <v>11</v>
       </c>
       <c r="E271" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F271" t="s">
         <v>19</v>
@@ -9709,10 +9709,10 @@
         <v>11</v>
       </c>
       <c r="E272" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F272" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G272" t="s">
         <v>14</v>
@@ -9741,10 +9741,10 @@
         <v>11</v>
       </c>
       <c r="E273" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F273" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G273" t="s">
         <v>15</v>
@@ -9840,7 +9840,7 @@
         <v>21</v>
       </c>
       <c r="F276" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G276" t="s">
         <v>14</v>
@@ -9869,7 +9869,7 @@
         <v>11</v>
       </c>
       <c r="E277" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F277" t="s">
         <v>21</v>
@@ -10288,7 +10288,7 @@
         <v>12</v>
       </c>
       <c r="F290" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G290" t="s">
         <v>14</v>
@@ -10317,7 +10317,7 @@
         <v>11</v>
       </c>
       <c r="E291" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F291" t="s">
         <v>12</v>
@@ -10413,10 +10413,10 @@
         <v>11</v>
       </c>
       <c r="E294" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F294" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G294" t="s">
         <v>15</v>
@@ -10445,10 +10445,10 @@
         <v>11</v>
       </c>
       <c r="E295" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F295" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G295" t="s">
         <v>14</v>
@@ -10477,7 +10477,7 @@
         <v>11</v>
       </c>
       <c r="E296" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F296" t="s">
         <v>22</v>
@@ -10512,7 +10512,7 @@
         <v>22</v>
       </c>
       <c r="F297" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G297" t="s">
         <v>14</v>
@@ -10541,10 +10541,10 @@
         <v>11</v>
       </c>
       <c r="E298" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F298" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G298" t="s">
         <v>15</v>
@@ -10573,10 +10573,10 @@
         <v>11</v>
       </c>
       <c r="E299" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F299" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G299" t="s">
         <v>14</v>
@@ -10605,10 +10605,10 @@
         <v>11</v>
       </c>
       <c r="E300" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F300" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G300" t="s">
         <v>14</v>
@@ -10637,10 +10637,10 @@
         <v>11</v>
       </c>
       <c r="E301" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F301" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G301" t="s">
         <v>15</v>
@@ -10733,7 +10733,7 @@
         <v>11</v>
       </c>
       <c r="E304" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F304" t="s">
         <v>17</v>
@@ -10768,7 +10768,7 @@
         <v>17</v>
       </c>
       <c r="F305" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G305" t="s">
         <v>15</v>
@@ -10864,7 +10864,7 @@
         <v>32</v>
       </c>
       <c r="F308" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G308" t="s">
         <v>15</v>
@@ -10893,7 +10893,7 @@
         <v>11</v>
       </c>
       <c r="E309" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F309" t="s">
         <v>32</v>
@@ -10989,10 +10989,10 @@
         <v>11</v>
       </c>
       <c r="E312" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F312" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G312" t="s">
         <v>15</v>
@@ -11021,10 +11021,10 @@
         <v>11</v>
       </c>
       <c r="E313" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F313" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G313" t="s">
         <v>14</v>
@@ -11181,7 +11181,7 @@
         <v>11</v>
       </c>
       <c r="E318" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F318" t="s">
         <v>22</v>
@@ -11216,7 +11216,7 @@
         <v>22</v>
       </c>
       <c r="F319" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G319" t="s">
         <v>15</v>
@@ -11309,10 +11309,10 @@
         <v>11</v>
       </c>
       <c r="E322" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F322" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G322" t="s">
         <v>15</v>
@@ -11341,10 +11341,10 @@
         <v>11</v>
       </c>
       <c r="E323" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F323" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G323" t="s">
         <v>14</v>
@@ -11373,10 +11373,10 @@
         <v>11</v>
       </c>
       <c r="E324" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F324" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G324" t="s">
         <v>15</v>
@@ -11405,10 +11405,10 @@
         <v>11</v>
       </c>
       <c r="E325" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F325" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G325" t="s">
         <v>14</v>
@@ -11437,7 +11437,7 @@
         <v>11</v>
       </c>
       <c r="E326" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F326" t="s">
         <v>27</v>
@@ -11472,7 +11472,7 @@
         <v>27</v>
       </c>
       <c r="F327" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G327" t="s">
         <v>14</v>
@@ -11501,7 +11501,7 @@
         <v>11</v>
       </c>
       <c r="E328" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F328" t="s">
         <v>13</v>
@@ -11536,7 +11536,7 @@
         <v>13</v>
       </c>
       <c r="F329" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G329" t="s">
         <v>15</v>
@@ -11629,7 +11629,7 @@
         <v>11</v>
       </c>
       <c r="E332" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F332" t="s">
         <v>22</v>
@@ -11664,7 +11664,7 @@
         <v>22</v>
       </c>
       <c r="F333" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G333" t="s">
         <v>14</v>
@@ -11696,7 +11696,7 @@
         <v>30</v>
       </c>
       <c r="F334" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G334" t="s">
         <v>14</v>
@@ -11725,7 +11725,7 @@
         <v>11</v>
       </c>
       <c r="E335" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F335" t="s">
         <v>30</v>
@@ -11757,10 +11757,10 @@
         <v>11</v>
       </c>
       <c r="E336" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F336" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G336" t="s">
         <v>14</v>
@@ -11789,10 +11789,10 @@
         <v>11</v>
       </c>
       <c r="E337" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F337" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G337" t="s">
         <v>15</v>
@@ -12141,10 +12141,10 @@
         <v>11</v>
       </c>
       <c r="E348" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F348" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G348" t="s">
         <v>15</v>
@@ -12173,10 +12173,10 @@
         <v>11</v>
       </c>
       <c r="E349" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F349" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G349" t="s">
         <v>14</v>
@@ -12205,7 +12205,7 @@
         <v>11</v>
       </c>
       <c r="E350" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F350" t="s">
         <v>18</v>
@@ -12240,7 +12240,7 @@
         <v>18</v>
       </c>
       <c r="F351" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G351" t="s">
         <v>14</v>
@@ -12269,7 +12269,7 @@
         <v>11</v>
       </c>
       <c r="E352" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F352" t="s">
         <v>23</v>
@@ -12304,7 +12304,7 @@
         <v>23</v>
       </c>
       <c r="F353" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G353" t="s">
         <v>15</v>
@@ -12336,7 +12336,7 @@
         <v>13</v>
       </c>
       <c r="F354" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G354" t="s">
         <v>14</v>
@@ -12365,7 +12365,7 @@
         <v>11</v>
       </c>
       <c r="E355" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F355" t="s">
         <v>13</v>
@@ -12397,10 +12397,10 @@
         <v>11</v>
       </c>
       <c r="E356" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F356" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G356" t="s">
         <v>15</v>
@@ -12429,10 +12429,10 @@
         <v>11</v>
       </c>
       <c r="E357" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F357" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G357" t="s">
         <v>14</v>
@@ -12464,7 +12464,7 @@
         <v>24</v>
       </c>
       <c r="F358" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G358" t="s">
         <v>14</v>
@@ -12493,7 +12493,7 @@
         <v>11</v>
       </c>
       <c r="E359" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F359" t="s">
         <v>24</v>
@@ -12589,10 +12589,10 @@
         <v>11</v>
       </c>
       <c r="E362" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F362" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G362" t="s">
         <v>15</v>
@@ -12621,10 +12621,10 @@
         <v>11</v>
       </c>
       <c r="E363" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F363" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G363" t="s">
         <v>14</v>
@@ -12656,7 +12656,7 @@
         <v>16</v>
       </c>
       <c r="F364" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G364" t="s">
         <v>14</v>
@@ -12685,7 +12685,7 @@
         <v>11</v>
       </c>
       <c r="E365" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F365" t="s">
         <v>16</v>
@@ -12784,7 +12784,7 @@
         <v>25</v>
       </c>
       <c r="F368" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G368" t="s">
         <v>15</v>
@@ -12813,7 +12813,7 @@
         <v>11</v>
       </c>
       <c r="E369" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F369" t="s">
         <v>25</v>
@@ -12909,7 +12909,7 @@
         <v>11</v>
       </c>
       <c r="E372" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F372" t="s">
         <v>22</v>
@@ -12944,7 +12944,7 @@
         <v>22</v>
       </c>
       <c r="F373" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G373" t="s">
         <v>15</v>
@@ -12973,10 +12973,10 @@
         <v>11</v>
       </c>
       <c r="E374" t="s">
+        <v>49</v>
+      </c>
+      <c r="F374" t="s">
         <v>37</v>
-      </c>
-      <c r="F374" t="s">
-        <v>39</v>
       </c>
       <c r="G374" t="s">
         <v>14</v>
@@ -13005,10 +13005,10 @@
         <v>11</v>
       </c>
       <c r="E375" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F375" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G375" t="s">
         <v>15</v>
@@ -13165,7 +13165,7 @@
         <v>11</v>
       </c>
       <c r="E380" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F380" t="s">
         <v>18</v>
@@ -13200,7 +13200,7 @@
         <v>18</v>
       </c>
       <c r="F381" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G381" t="s">
         <v>14</v>
@@ -13232,7 +13232,7 @@
         <v>30</v>
       </c>
       <c r="F382" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G382" t="s">
         <v>14</v>
@@ -13261,7 +13261,7 @@
         <v>11</v>
       </c>
       <c r="E383" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F383" t="s">
         <v>30</v>
@@ -13421,7 +13421,7 @@
         <v>11</v>
       </c>
       <c r="E388" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F388" t="s">
         <v>31</v>
@@ -13456,7 +13456,7 @@
         <v>31</v>
       </c>
       <c r="F389" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G389" t="s">
         <v>15</v>
@@ -13805,7 +13805,7 @@
         <v>11</v>
       </c>
       <c r="E400" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F400" t="s">
         <v>25</v>
@@ -13840,7 +13840,7 @@
         <v>25</v>
       </c>
       <c r="F401" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G401" t="s">
         <v>14</v>
@@ -13872,7 +13872,7 @@
         <v>24</v>
       </c>
       <c r="F402" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G402" t="s">
         <v>15</v>
@@ -13901,7 +13901,7 @@
         <v>11</v>
       </c>
       <c r="E403" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F403" t="s">
         <v>24</v>
@@ -13936,7 +13936,7 @@
         <v>27</v>
       </c>
       <c r="F404" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G404" t="s">
         <v>14</v>
@@ -13965,7 +13965,7 @@
         <v>11</v>
       </c>
       <c r="E405" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F405" t="s">
         <v>27</v>
@@ -14000,7 +14000,7 @@
         <v>30</v>
       </c>
       <c r="F406" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G406" t="s">
         <v>15</v>
@@ -14029,7 +14029,7 @@
         <v>11</v>
       </c>
       <c r="E407" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F407" t="s">
         <v>30</v>
@@ -14061,7 +14061,7 @@
         <v>11</v>
       </c>
       <c r="E408" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F408" t="s">
         <v>13</v>
@@ -14096,7 +14096,7 @@
         <v>13</v>
       </c>
       <c r="F409" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G409" t="s">
         <v>15</v>
@@ -14125,10 +14125,10 @@
         <v>11</v>
       </c>
       <c r="E410" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F410" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G410" t="s">
         <v>14</v>
@@ -14157,10 +14157,10 @@
         <v>11</v>
       </c>
       <c r="E411" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F411" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G411" t="s">
         <v>15</v>
@@ -14189,10 +14189,10 @@
         <v>11</v>
       </c>
       <c r="E412" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F412" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G412" t="s">
         <v>15</v>
@@ -14221,10 +14221,10 @@
         <v>11</v>
       </c>
       <c r="E413" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F413" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G413" t="s">
         <v>14</v>
@@ -14253,7 +14253,7 @@
         <v>11</v>
       </c>
       <c r="E414" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F414" t="s">
         <v>32</v>
@@ -14288,7 +14288,7 @@
         <v>32</v>
       </c>
       <c r="F415" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G415" t="s">
         <v>14</v>
@@ -14320,7 +14320,7 @@
         <v>29</v>
       </c>
       <c r="F416" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G416" t="s">
         <v>14</v>
@@ -14349,7 +14349,7 @@
         <v>11</v>
       </c>
       <c r="E417" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F417" t="s">
         <v>29</v>
@@ -14381,10 +14381,10 @@
         <v>11</v>
       </c>
       <c r="E418" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F418" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G418" t="s">
         <v>15</v>
@@ -14413,10 +14413,10 @@
         <v>11</v>
       </c>
       <c r="E419" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F419" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G419" t="s">
         <v>14</v>
@@ -14576,7 +14576,7 @@
         <v>12</v>
       </c>
       <c r="F424" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G424" t="s">
         <v>15</v>
@@ -14605,7 +14605,7 @@
         <v>11</v>
       </c>
       <c r="E425" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F425" t="s">
         <v>12</v>
@@ -14896,7 +14896,7 @@
         <v>13</v>
       </c>
       <c r="F434" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G434" t="s">
         <v>14</v>
@@ -14925,7 +14925,7 @@
         <v>11</v>
       </c>
       <c r="E435" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F435" t="s">
         <v>13</v>
@@ -14957,10 +14957,10 @@
         <v>11</v>
       </c>
       <c r="E436" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F436" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G436" t="s">
         <v>15</v>
@@ -14989,10 +14989,10 @@
         <v>11</v>
       </c>
       <c r="E437" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F437" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G437" t="s">
         <v>14</v>
@@ -15024,7 +15024,7 @@
         <v>28</v>
       </c>
       <c r="F438" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G438" t="s">
         <v>15</v>
@@ -15053,7 +15053,7 @@
         <v>11</v>
       </c>
       <c r="E439" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F439" t="s">
         <v>28</v>
@@ -15149,7 +15149,7 @@
         <v>11</v>
       </c>
       <c r="E442" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F442" t="s">
         <v>22</v>
@@ -15184,7 +15184,7 @@
         <v>22</v>
       </c>
       <c r="F443" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G443" t="s">
         <v>14</v>
@@ -15213,10 +15213,10 @@
         <v>11</v>
       </c>
       <c r="E444" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F444" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G444" t="s">
         <v>15</v>
@@ -15245,10 +15245,10 @@
         <v>11</v>
       </c>
       <c r="E445" t="s">
+        <v>39</v>
+      </c>
+      <c r="F445" t="s">
         <v>42</v>
-      </c>
-      <c r="F445" t="s">
-        <v>45</v>
       </c>
       <c r="G445" t="s">
         <v>14</v>
@@ -15341,10 +15341,10 @@
         <v>11</v>
       </c>
       <c r="E448" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F448" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G448" t="s">
         <v>15</v>
@@ -15373,10 +15373,10 @@
         <v>11</v>
       </c>
       <c r="E449" t="s">
+        <v>36</v>
+      </c>
+      <c r="F449" t="s">
         <v>38</v>
-      </c>
-      <c r="F449" t="s">
-        <v>41</v>
       </c>
       <c r="G449" t="s">
         <v>14</v>
@@ -15405,7 +15405,7 @@
         <v>11</v>
       </c>
       <c r="E450" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F450" t="s">
         <v>28</v>
@@ -15440,7 +15440,7 @@
         <v>28</v>
       </c>
       <c r="F451" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G451" t="s">
         <v>14</v>
@@ -15533,10 +15533,10 @@
         <v>11</v>
       </c>
       <c r="E454" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F454" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G454" t="s">
         <v>14</v>
@@ -15565,10 +15565,10 @@
         <v>11</v>
       </c>
       <c r="E455" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F455" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G455" t="s">
         <v>15</v>
@@ -15853,7 +15853,7 @@
         <v>11</v>
       </c>
       <c r="E464" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F464" t="s">
         <v>22</v>
@@ -15888,7 +15888,7 @@
         <v>22</v>
       </c>
       <c r="F465" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G465" t="s">
         <v>14</v>
@@ -15917,7 +15917,7 @@
         <v>11</v>
       </c>
       <c r="E466" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F466" t="s">
         <v>29</v>
@@ -15952,7 +15952,7 @@
         <v>29</v>
       </c>
       <c r="F467" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G467" t="s">
         <v>15</v>
@@ -16109,10 +16109,10 @@
         <v>11</v>
       </c>
       <c r="E472" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F472" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G472" t="s">
         <v>15</v>
@@ -16141,10 +16141,10 @@
         <v>11</v>
       </c>
       <c r="E473" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F473" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G473" t="s">
         <v>14</v>
@@ -16173,10 +16173,10 @@
         <v>11</v>
       </c>
       <c r="E474" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F474" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G474" t="s">
         <v>14</v>
@@ -16205,10 +16205,10 @@
         <v>11</v>
       </c>
       <c r="E475" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F475" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G475" t="s">
         <v>15</v>
@@ -16237,7 +16237,7 @@
         <v>11</v>
       </c>
       <c r="E476" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F476" t="s">
         <v>13</v>
@@ -16272,7 +16272,7 @@
         <v>13</v>
       </c>
       <c r="F477" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G477" t="s">
         <v>15</v>
@@ -16301,10 +16301,10 @@
         <v>11</v>
       </c>
       <c r="E478" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F478" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G478" t="s">
         <v>15</v>
@@ -16333,10 +16333,10 @@
         <v>11</v>
       </c>
       <c r="E479" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F479" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G479" t="s">
         <v>14</v>
@@ -16432,7 +16432,7 @@
         <v>18</v>
       </c>
       <c r="F482" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G482" t="s">
         <v>15</v>
@@ -16461,7 +16461,7 @@
         <v>11</v>
       </c>
       <c r="E483" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F483" t="s">
         <v>18</v>
@@ -16493,7 +16493,7 @@
         <v>11</v>
       </c>
       <c r="E484" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F484" t="s">
         <v>12</v>
@@ -16528,7 +16528,7 @@
         <v>12</v>
       </c>
       <c r="F485" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G485" t="s">
         <v>14</v>
@@ -16621,10 +16621,10 @@
         <v>11</v>
       </c>
       <c r="E488" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F488" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G488" t="s">
         <v>15</v>
@@ -16653,10 +16653,10 @@
         <v>11</v>
       </c>
       <c r="E489" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F489" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G489" t="s">
         <v>14</v>
@@ -16752,7 +16752,7 @@
         <v>21</v>
       </c>
       <c r="F492" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G492" t="s">
         <v>15</v>
@@ -16781,7 +16781,7 @@
         <v>11</v>
       </c>
       <c r="E493" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F493" t="s">
         <v>21</v>
@@ -16816,7 +16816,7 @@
         <v>23</v>
       </c>
       <c r="F494" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G494" t="s">
         <v>14</v>
@@ -16845,7 +16845,7 @@
         <v>11</v>
       </c>
       <c r="E495" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F495" t="s">
         <v>23</v>
@@ -16944,7 +16944,7 @@
         <v>24</v>
       </c>
       <c r="F498" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G498" t="s">
         <v>15</v>
@@ -16973,7 +16973,7 @@
         <v>11</v>
       </c>
       <c r="E499" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F499" t="s">
         <v>24</v>
@@ -17069,10 +17069,10 @@
         <v>11</v>
       </c>
       <c r="E502" t="s">
+        <v>50</v>
+      </c>
+      <c r="F502" t="s">
         <v>40</v>
-      </c>
-      <c r="F502" t="s">
-        <v>43</v>
       </c>
       <c r="G502" t="s">
         <v>14</v>
@@ -17101,10 +17101,10 @@
         <v>11</v>
       </c>
       <c r="E503" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F503" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G503" t="s">
         <v>15</v>
@@ -17200,7 +17200,7 @@
         <v>31</v>
       </c>
       <c r="F506" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G506" t="s">
         <v>14</v>
@@ -17229,7 +17229,7 @@
         <v>11</v>
       </c>
       <c r="E507" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F507" t="s">
         <v>31</v>
@@ -17325,10 +17325,10 @@
         <v>11</v>
       </c>
       <c r="E510" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F510" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G510" t="s">
         <v>15</v>
@@ -17357,10 +17357,10 @@
         <v>11</v>
       </c>
       <c r="E511" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F511" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G511" t="s">
         <v>14</v>
@@ -17901,10 +17901,10 @@
         <v>11</v>
       </c>
       <c r="E528" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F528" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G528" t="s">
         <v>14</v>
@@ -17933,10 +17933,10 @@
         <v>11</v>
       </c>
       <c r="E529" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F529" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G529" t="s">
         <v>15</v>
@@ -18029,7 +18029,7 @@
         <v>11</v>
       </c>
       <c r="E532" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F532" t="s">
         <v>23</v>
@@ -18064,7 +18064,7 @@
         <v>23</v>
       </c>
       <c r="F533" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G533" t="s">
         <v>15</v>
@@ -18093,7 +18093,7 @@
         <v>11</v>
       </c>
       <c r="E534" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F534" t="s">
         <v>22</v>
@@ -18128,7 +18128,7 @@
         <v>22</v>
       </c>
       <c r="F535" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G535" t="s">
         <v>15</v>
@@ -18157,10 +18157,10 @@
         <v>11</v>
       </c>
       <c r="E536" t="s">
+        <v>51</v>
+      </c>
+      <c r="F536" t="s">
         <v>34</v>
-      </c>
-      <c r="F536" t="s">
-        <v>35</v>
       </c>
       <c r="G536" t="s">
         <v>15</v>
@@ -18189,10 +18189,10 @@
         <v>11</v>
       </c>
       <c r="E537" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F537" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="G537" t="s">
         <v>14</v>
@@ -18224,7 +18224,7 @@
         <v>13</v>
       </c>
       <c r="F538" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="G538" t="s">
         <v>14</v>
@@ -18253,7 +18253,7 @@
         <v>11</v>
       </c>
       <c r="E539" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="F539" t="s">
         <v>13</v>
@@ -18285,10 +18285,10 @@
         <v>11</v>
       </c>
       <c r="E540" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F540" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G540" t="s">
         <v>15</v>
@@ -18317,10 +18317,10 @@
         <v>11</v>
       </c>
       <c r="E541" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F541" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G541" t="s">
         <v>14</v>
@@ -18349,7 +18349,7 @@
         <v>11</v>
       </c>
       <c r="E542" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F542" t="s">
         <v>30</v>
@@ -18384,7 +18384,7 @@
         <v>30</v>
       </c>
       <c r="F543" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G543" t="s">
         <v>15</v>
@@ -18413,10 +18413,10 @@
         <v>11</v>
       </c>
       <c r="E544" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F544" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G544" t="s">
         <v>14</v>
@@ -18445,10 +18445,10 @@
         <v>11</v>
       </c>
       <c r="E545" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F545" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G545" t="s">
         <v>15</v>
@@ -18471,10 +18471,10 @@
         <v>2023</v>
       </c>
       <c r="C546" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D546" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E546" t="s">
         <v>25</v>
@@ -18503,10 +18503,10 @@
         <v>2023</v>
       </c>
       <c r="C547" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D547" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E547" t="s">
         <v>18</v>
@@ -18535,16 +18535,16 @@
         <v>2023</v>
       </c>
       <c r="C548" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D548" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E548" t="s">
         <v>13</v>
       </c>
       <c r="F548" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G548" t="s">
         <v>15</v>
@@ -18567,13 +18567,13 @@
         <v>2023</v>
       </c>
       <c r="C549" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D549" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E549" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F549" t="s">
         <v>13</v>
@@ -18599,16 +18599,16 @@
         <v>2023</v>
       </c>
       <c r="C550" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D550" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E550" t="s">
         <v>32</v>
       </c>
       <c r="F550" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G550" t="s">
         <v>14</v>
@@ -18631,13 +18631,13 @@
         <v>2023</v>
       </c>
       <c r="C551" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D551" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E551" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F551" t="s">
         <v>32</v>
@@ -18663,16 +18663,16 @@
         <v>2023</v>
       </c>
       <c r="C552" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D552" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E552" t="s">
         <v>12</v>
       </c>
       <c r="F552" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G552" t="s">
         <v>15</v>
@@ -18695,13 +18695,13 @@
         <v>2023</v>
       </c>
       <c r="C553" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D553" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E553" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F553" t="s">
         <v>12</v>
@@ -18727,13 +18727,13 @@
         <v>2023</v>
       </c>
       <c r="C554" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D554" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E554" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F554" t="s">
         <v>31</v>
@@ -18759,16 +18759,16 @@
         <v>2023</v>
       </c>
       <c r="C555" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D555" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E555" t="s">
         <v>31</v>
       </c>
       <c r="F555" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G555" t="s">
         <v>14</v>
@@ -18791,16 +18791,16 @@
         <v>2023</v>
       </c>
       <c r="C556" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D556" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E556" t="s">
         <v>26</v>
       </c>
       <c r="F556" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G556" t="s">
         <v>15</v>
@@ -18823,13 +18823,13 @@
         <v>2023</v>
       </c>
       <c r="C557" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D557" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E557" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F557" t="s">
         <v>26</v>
@@ -18855,10 +18855,10 @@
         <v>2023</v>
       </c>
       <c r="C558" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D558" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E558" t="s">
         <v>24</v>
@@ -18887,10 +18887,10 @@
         <v>2023</v>
       </c>
       <c r="C559" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D559" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E559" t="s">
         <v>25</v>
@@ -18919,10 +18919,10 @@
         <v>2023</v>
       </c>
       <c r="C560" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D560" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E560" t="s">
         <v>30</v>
@@ -18951,10 +18951,10 @@
         <v>2023</v>
       </c>
       <c r="C561" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D561" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E561" t="s">
         <v>32</v>
@@ -18983,10 +18983,10 @@
         <v>2023</v>
       </c>
       <c r="C562" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D562" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E562" t="s">
         <v>12</v>
@@ -19015,10 +19015,10 @@
         <v>2023</v>
       </c>
       <c r="C563" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D563" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E563" t="s">
         <v>26</v>
@@ -19047,16 +19047,16 @@
         <v>2023</v>
       </c>
       <c r="C564" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D564" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E564" t="s">
         <v>13</v>
       </c>
       <c r="F564" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G564" t="s">
         <v>14</v>
@@ -19079,13 +19079,13 @@
         <v>2023</v>
       </c>
       <c r="C565" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D565" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E565" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F565" t="s">
         <v>13</v>
@@ -19111,10 +19111,10 @@
         <v>2023</v>
       </c>
       <c r="C566" t="s">
+        <v>43</v>
+      </c>
+      <c r="D566" t="s">
         <v>46</v>
-      </c>
-      <c r="D566" t="s">
-        <v>49</v>
       </c>
       <c r="E566" t="s">
         <v>13</v>
@@ -19143,10 +19143,10 @@
         <v>2023</v>
       </c>
       <c r="C567" t="s">
+        <v>43</v>
+      </c>
+      <c r="D567" t="s">
         <v>46</v>
-      </c>
-      <c r="D567" t="s">
-        <v>49</v>
       </c>
       <c r="E567" t="s">
         <v>24</v>
@@ -19175,10 +19175,10 @@
         <v>2023</v>
       </c>
       <c r="C568" t="s">
+        <v>43</v>
+      </c>
+      <c r="D568" t="s">
         <v>46</v>
-      </c>
-      <c r="D568" t="s">
-        <v>49</v>
       </c>
       <c r="E568" t="s">
         <v>30</v>
@@ -19207,10 +19207,10 @@
         <v>2023</v>
       </c>
       <c r="C569" t="s">
+        <v>43</v>
+      </c>
+      <c r="D569" t="s">
         <v>46</v>
-      </c>
-      <c r="D569" t="s">
-        <v>49</v>
       </c>
       <c r="E569" t="s">
         <v>12</v>
@@ -19239,10 +19239,10 @@
         <v>2023</v>
       </c>
       <c r="C570" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D570" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E570" t="s">
         <v>13</v>
@@ -19251,7 +19251,7 @@
         <v>30</v>
       </c>
       <c r="G570" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H570">
         <v>25</v>
@@ -19271,10 +19271,10 @@
         <v>2023</v>
       </c>
       <c r="C571" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D571" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E571" t="s">
         <v>30</v>
@@ -19283,7 +19283,7 @@
         <v>13</v>
       </c>
       <c r="G571" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="H571">
         <v>22</v>
